--- a/battrymenu.xlsx
+++ b/battrymenu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\program\produksi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771C6D1D-FD60-46D4-9263-2D409641B6CC}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B51AF5-D378-4281-862B-3F7A40DB788A}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{654B69ED-63D0-4E9B-ABE2-64DA5ED5B105}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="10">
   <si>
     <t>Eve</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>A-50L</t>
+  </si>
+  <si>
+    <t>CX</t>
+  </si>
+  <si>
+    <t>A-32700</t>
   </si>
 </sst>
 </file>
@@ -415,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A24BFE31-0D20-4C82-8CA8-B641B905431B}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -494,11 +500,25 @@
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
